--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:20.806Z</t>
+    <t>2026-10-02T04:13:59.608Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:59.608Z</t>
+    <t>2026-10-02T15:08:52.234Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:52.234Z</t>
+    <t>2026-10-02T15:30:07.160Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:30:07.160Z</t>
+    <t>2026-10-02T16:18:52.192Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:52.192Z</t>
+    <t>2026-10-02T19:28:14.554Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:28:14.554Z</t>
+    <t>2026-10-02T19:44:35.379Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -2112,7 +2112,7 @@
     <t>expiresAt - createdAt = 30 min; timeout behaviour shown; no reservation exists</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-122, BR-122</t>
+    <t>AQPI-15, REQ-122, BR-122</t>
   </si>
   <si>
     <t>TC-F-113</t>
@@ -2138,7 +2138,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2177,7 +2177,7 @@
     <t>First 3 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml, REQ-124, BR-124</t>
+    <t>AQPI-26, REQ-124, BR-124</t>
   </si>
   <si>
     <t>TC-F-116</t>
@@ -2196,7 +2196,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -2246,7 +2246,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-126, BR-126</t>
+    <t>AQPI-4, REQ-126, BR-126</t>
   </si>
   <si>
     <t>TC-F-120</t>
@@ -2312,7 +2312,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -2384,7 +2384,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:35.379Z</t>
+    <t>2026-10-02T20:05:34.021Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:34.021Z</t>
+    <t>2026-10-02T20:26:37.600Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/04-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:37.600Z</t>
+    <t>2026-10-02T20:29:20.305Z</t>
   </si>
   <si>
     <t>Column order</t>
